--- a/ExcelProject/ReviewCourse.xlsx
+++ b/ExcelProject/ReviewCourse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
   <si>
     <t>Execute</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Result</t>
   </si>
   <si>
+    <t>Revise</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -61,10 +64,7 @@
     <t>ขอบคุณสำหรับการแสดงความคิดเห็น</t>
   </si>
   <si>
-    <t>บันทึกรีวิวสำเร็จ</t>
-  </si>
-  <si>
-    <t>Fail</t>
+    <t/>
   </si>
   <si>
     <t>N</t>
@@ -91,13 +91,13 @@
     <t>TC9:05</t>
   </si>
   <si>
-    <t>MJU6504106418</t>
+    <t>MJU6504106420</t>
   </si>
   <si>
     <t>TC9:06</t>
   </si>
   <si>
-    <t>MJU6504106419</t>
+    <t>MJU6504106423</t>
   </si>
   <si>
     <t>กรุณาให้คะแนน</t>
@@ -106,13 +106,13 @@
     <t>TC9:07</t>
   </si>
   <si>
-    <t>MJU6504106420</t>
+    <t>MJU6504106424</t>
   </si>
   <si>
     <t>TC9:08</t>
   </si>
   <si>
-    <t>MJU6504106421</t>
+    <t>MJU6504106425</t>
   </si>
   <si>
     <t>VeryGood</t>
@@ -121,7 +121,7 @@
     <t>TC9:09</t>
   </si>
   <si>
-    <t>MJU6504106422</t>
+    <t>MJU6504106426</t>
   </si>
   <si>
     <t>วิทยาศาสตร์เป็นหนึ่งในวิชาที่มีความสำคัญอย่างยิ่งต่อมนุษยชาติ!!</t>
@@ -133,7 +133,7 @@
     <t>TC9:10</t>
   </si>
   <si>
-    <t>MJU6504106423</t>
+    <t>MJU6504106428</t>
   </si>
   <si>
     <t>D</t>
@@ -142,7 +142,7 @@
     <t>TC9:11</t>
   </si>
   <si>
-    <t>MJU6504106424</t>
+    <t>MJU6504106430</t>
   </si>
   <si>
     <t>VG</t>
@@ -151,7 +151,7 @@
     <t>TC9:12</t>
   </si>
   <si>
-    <t>MJU6504106425</t>
+    <t>MJU6504106432</t>
   </si>
   <si>
     <t>เป็นประโยชน์มากในการหาข้อผิดพลาดที่อาจเกิดขึ้นในกรณีที่โปรแกรมทำงานใกล้ค่าขอบเขตของอินพุตช่วยให้เรามองเห็นถึงความละเอียดและความรอบคอบที่จำเป็นต่อการพัฒนาระบบซอฟต์แวร์ที่มีประสิทธิภาพ อีกทั้งยังได้ฝึกทักษะการคิดวิเคราะห์และการเขียนโปรแกรมควบคู่กับการทดสอบ</t>
@@ -160,7 +160,7 @@
     <t>TC9:13</t>
   </si>
   <si>
-    <t>MJU6504106426</t>
+    <t>MJU6504106436</t>
   </si>
   <si>
     <t>เป็นประโยชน์มากในการหาข้อผิดพลาดที่อาจเกิดขึ้นในกรณีที่โปรแกรมทำงานใกล้ค่าขอบเขตของอินพุต ช่วยให้เรามองเห็นถึงความละเอียดและความรอบคอบที่จำเป็นต่อการพัฒนาระบบซอฟต์แวร์ที่มีประสิทธิภาพ อีกทั้งยังได้ฝึกทักษะการคิดวิเคราะห์และการเขียนโปรแกรมควบคู่กับการทดสอบ</t>
@@ -169,7 +169,7 @@
     <t>TC9:14</t>
   </si>
   <si>
-    <t>MJU6504106427</t>
+    <t>MJU6504106444</t>
   </si>
   <si>
     <t>เป็นประโยชน์มากในการหาข้อผิดพลาดที่อาจเกิดขึ้นในกรณีที่โปรแกรมทำงานใกล้ค่าขอบเขตของอินพุตช่วยให้เรามองเห็นถึงความละเอียดและความรอบคอบที่จำเป็นต่อการพัฒนาระบบซอฟต์แวร์ที่มีประสิทธิภาพ อีกทั้งยังได้ฝึกทักษะการคิดวิเคราะห์และการเขียนโปรแกรมควบคู่กับการทดสอบวิ</t>
@@ -181,7 +181,7 @@
     <t>TC9:15</t>
   </si>
   <si>
-    <t>MJU6504106428</t>
+    <t>MJU6504106449</t>
   </si>
   <si>
     <t>It Very Good</t>
@@ -190,7 +190,7 @@
     <t>TC9:16</t>
   </si>
   <si>
-    <t>MJU6504106429</t>
+    <t>MJU6504106451</t>
   </si>
   <si>
     <t>กรุณากรอกความคิดเห็น</t>
@@ -268,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,6 +286,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -608,18 +611,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="169.57642857142858" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="33.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="11" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="170.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="11" width="33.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="11" width="18.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27">
@@ -650,33 +654,37 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
       <c r="A2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -691,21 +699,22 @@
         <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="6">
         <v>2</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -720,21 +729,22 @@
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="6">
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -749,21 +759,22 @@
         <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6">
         <v>4</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -778,21 +789,22 @@
         <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -807,17 +819,18 @@
         <v>27</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="E7" s="8"/>
       <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
       <c r="A8" s="5" t="s">
@@ -830,21 +843,22 @@
         <v>30</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="6">
         <v>5</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -859,7 +873,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="6">
         <v>5</v>
@@ -868,12 +882,13 @@
         <v>33</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="H9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -888,21 +903,22 @@
         <v>35</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="6">
         <v>5</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -917,7 +933,7 @@
         <v>39</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="6">
         <v>5</v>
@@ -926,12 +942,13 @@
         <v>40</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="H11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -946,7 +963,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="6">
         <v>5</v>
@@ -955,12 +972,13 @@
         <v>43</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="H12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -975,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="6">
         <v>5</v>
@@ -984,10 +1002,11 @@
         <v>46</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
       <c r="A14" s="5" t="s">
@@ -1000,7 +1019,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="6">
         <v>5</v>
@@ -1009,10 +1028,11 @@
         <v>49</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
       <c r="A15" s="5" t="s">
@@ -1025,12 +1045,12 @@
         <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="6">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="5" t="s">
@@ -1038,6 +1058,7 @@
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
       <c r="A16" s="5" t="s">
@@ -1050,7 +1071,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="6">
         <v>5</v>
@@ -1059,10 +1080,11 @@
         <v>56</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
       <c r="A17" s="5" t="s">
@@ -1075,17 +1097,18 @@
         <v>58</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="6">
         <v>5</v>
       </c>
-      <c r="F17" s="9"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="5" t="s">
         <v>59</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelProject/ReviewCourse.xlsx
+++ b/ExcelProject/ReviewCourse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="61">
   <si>
     <t>Execute</t>
   </si>
@@ -61,13 +61,10 @@
     <t>วิทยาศาสตร์เป็นหนึ่งในวิชาที่มีความสำคัญอย่างยิ่งต่อมนุษยชาติ</t>
   </si>
   <si>
-    <t>ขอบคุณสำหรับการแสดงความคิดเห็น</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>N</t>
+    <t>รีวิวคอร์สสำเร็จ</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>TC9:02</t>
@@ -100,7 +97,7 @@
     <t>MJU6504106423</t>
   </si>
   <si>
-    <t>กรุณาให้คะแนน</t>
+    <t>กรุณาเลือกจำนวนดาวก่อนส่ง ⭐</t>
   </si>
   <si>
     <t>TC9:07</t>
@@ -130,6 +127,9 @@
     <t>กรุณากรอกข้อมูลเป็นภาษาไทยหรือภาษาอังกฤษ</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>TC9:10</t>
   </si>
   <si>
@@ -157,6 +157,9 @@
     <t>เป็นประโยชน์มากในการหาข้อผิดพลาดที่อาจเกิดขึ้นในกรณีที่โปรแกรมทำงานใกล้ค่าขอบเขตของอินพุตช่วยให้เรามองเห็นถึงความละเอียดและความรอบคอบที่จำเป็นต่อการพัฒนาระบบซอฟต์แวร์ที่มีประสิทธิภาพ อีกทั้งยังได้ฝึกทักษะการคิดวิเคราะห์และการเขียนโปรแกรมควบคู่กับการทดสอบ</t>
   </si>
   <si>
+    <t>ไม่สามารถบันทึกได้</t>
+  </si>
+  <si>
     <t>TC9:13</t>
   </si>
   <si>
@@ -175,7 +178,7 @@
     <t>เป็นประโยชน์มากในการหาข้อผิดพลาดที่อาจเกิดขึ้นในกรณีที่โปรแกรมทำงานใกล้ค่าขอบเขตของอินพุตช่วยให้เรามองเห็นถึงความละเอียดและความรอบคอบที่จำเป็นต่อการพัฒนาระบบซอฟต์แวร์ที่มีประสิทธิภาพ อีกทั้งยังได้ฝึกทักษะการคิดวิเคราะห์และการเขียนโปรแกรมควบคู่กับการทดสอบวิ</t>
   </si>
   <si>
-    <t>กรุณากรอกได้ไม่เกิน 255 ตัวอักษร</t>
+    <t>ข้อความรีวิวต้องไม่เกิน 255 ตัวอักษร</t>
   </si>
   <si>
     <t>TC9:15</t>
@@ -268,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,9 +289,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -614,19 +614,19 @@
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="9.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="170.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="33.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="18.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="9.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="10.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="170.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="33.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="22.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="27.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="21">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
@@ -680,23 +680,25 @@
       <c r="G2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
       <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>13</v>
@@ -710,23 +712,25 @@
       <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21.75">
+      <c r="H3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="21">
       <c r="A4" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
@@ -740,23 +744,25 @@
       <c r="G4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21.75">
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>13</v>
@@ -770,23 +776,25 @@
       <c r="G5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21.75">
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="21">
       <c r="A6" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>13</v>
@@ -800,47 +808,55 @@
       <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="21.75">
+      <c r="H6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22.5">
       <c r="A7" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="21.75">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
@@ -854,23 +870,25 @@
       <c r="G8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21.75">
+      <c r="H8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
       <c r="A9" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>13</v>
@@ -879,28 +897,30 @@
         <v>5</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21.75">
-      <c r="A10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>13</v>
@@ -908,23 +928,25 @@
       <c r="E10" s="6">
         <v>5</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21.75">
+      <c r="J10" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="21">
       <c r="A11" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>38</v>
@@ -944,17 +966,19 @@
       <c r="G11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21.75">
+      <c r="H11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="21">
       <c r="A12" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>41</v>
@@ -974,17 +998,19 @@
       <c r="G12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21.75">
+      <c r="H12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="21">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>44</v>
@@ -1004,19 +1030,25 @@
       <c r="G13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21.75">
+      <c r="H13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21">
       <c r="A14" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>13</v>
@@ -1025,24 +1057,30 @@
         <v>5</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21.75">
+      <c r="H14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21">
       <c r="A15" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>13</v>
@@ -1050,25 +1088,31 @@
       <c r="E15" s="6">
         <v>5</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>52</v>
+      <c r="F15" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21.75">
+        <v>54</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21">
       <c r="A16" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>13</v>
@@ -1077,24 +1121,30 @@
         <v>5</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="22.5">
+      <c r="H16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21.75">
       <c r="A17" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>13</v>
@@ -1102,13 +1152,19 @@
       <c r="E17" s="6">
         <v>5</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
